--- a/evaluation/results.xlsx
+++ b/evaluation/results.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The arbitration proceedings will be conducted in Kanpur.</t>
+          <t>The arbitration proceedings will be conducted at Kanpur.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>The arbitrator, who is appointed by the Deputy Director of the Institute, conducts arbitration.</t>
+          <t>The arbitrator, who is appointed by the Deputy Director of the Institute, conducts the arbitration.</t>
         </is>
       </c>
     </row>
